--- a/artfynd/A 8265-2023 artfynd.xlsx
+++ b/artfynd/A 8265-2023 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118250928</v>
+        <v>118250963</v>
       </c>
       <c r="B3" t="n">
         <v>97733</v>
@@ -822,13 +822,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>721315</v>
+        <v>721316</v>
       </c>
       <c r="R3" t="n">
-        <v>6382524</v>
+        <v>6382559</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118251170</v>
+        <v>118251123</v>
       </c>
       <c r="B4" t="n">
         <v>97733</v>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>721268</v>
+        <v>721305</v>
       </c>
       <c r="R4" t="n">
-        <v>6382428</v>
+        <v>6382451</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -960,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-07-06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118251123</v>
+        <v>118251035</v>
       </c>
       <c r="B5" t="n">
-        <v>97733</v>
+        <v>97872</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>49</v>
+        <v>222118</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Salepsrot</t>
+          <t>Flugblomster</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anacamptis pyramidalis</t>
+          <t>Ophrys insectifera</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,13 +1026,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>721305</v>
+        <v>721315</v>
       </c>
       <c r="R5" t="n">
-        <v>6382451</v>
+        <v>6382550</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118251288</v>
+        <v>118251170</v>
       </c>
       <c r="B6" t="n">
-        <v>97869</v>
+        <v>97733</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219847</v>
+        <v>49</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Salepsrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Anacamptis pyramidalis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,13 +1128,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>721233</v>
+        <v>721268</v>
       </c>
       <c r="R6" t="n">
-        <v>6382420</v>
+        <v>6382428</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1200,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118251035</v>
+        <v>118251288</v>
       </c>
       <c r="B7" t="n">
-        <v>97872</v>
+        <v>97869</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222118</v>
+        <v>219847</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Flugblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ophrys insectifera</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,13 +1235,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>721315</v>
+        <v>721233</v>
       </c>
       <c r="R7" t="n">
-        <v>6382550</v>
+        <v>6382420</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1276,6 +1271,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,7 +1302,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118250963</v>
+        <v>118250928</v>
       </c>
       <c r="B8" t="n">
         <v>97733</v>
@@ -1342,13 +1342,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>721316</v>
+        <v>721315</v>
       </c>
       <c r="R8" t="n">
-        <v>6382559</v>
+        <v>6382524</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>

--- a/artfynd/A 8265-2023 artfynd.xlsx
+++ b/artfynd/A 8265-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118251257</v>
+        <v>118250928</v>
       </c>
       <c r="B2" t="n">
-        <v>97821</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99005</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219797</v>
+        <v>49</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Salepsrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Anacamptis pyramidalis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Aurungs (Aurungs), Gtl</t>
+          <t>Aurungs, Aurungs, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>721247</v>
+        <v>721315</v>
       </c>
       <c r="R2" t="n">
-        <v>6382420</v>
+        <v>6382524</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-07-06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,12 +775,7 @@
         <v>118250963</v>
       </c>
       <c r="B3" t="n">
-        <v>97733</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99005</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -818,7 +803,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Aurungs (Aurungs), Gtl</t>
+          <t>Aurungs, Aurungs, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -887,12 +872,7 @@
         <v>118251123</v>
       </c>
       <c r="B4" t="n">
-        <v>97733</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99005</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,7 +900,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Aurungs (Aurungs), Gtl</t>
+          <t>Aurungs, Aurungs, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -986,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118251035</v>
+        <v>118251170</v>
       </c>
       <c r="B5" t="n">
-        <v>97872</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99005</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,34 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222118</v>
+        <v>49</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Flugblomster</t>
+          <t>Salepsrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ophrys insectifera</t>
+          <t>Anacamptis pyramidalis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Aurungs (Aurungs), Gtl</t>
+          <t>Aurungs, Aurungs, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>721315</v>
+        <v>721268</v>
       </c>
       <c r="R5" t="n">
-        <v>6382550</v>
+        <v>6382428</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1062,6 +1037,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,53 +1068,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118251170</v>
+        <v>105082296</v>
       </c>
       <c r="B6" t="n">
-        <v>97733</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111405</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>49</v>
+        <v>219719</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Salepsrot</t>
+          <t>Säfferot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anacamptis pyramidalis</t>
+          <t>Seseli libanotis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) W. D. J. Koch</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Aurungs (Aurungs), Gtl</t>
+          <t>Aurungs 1050 m N, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>721268</v>
+        <v>721324</v>
       </c>
       <c r="R6" t="n">
-        <v>6382428</v>
+        <v>6382371</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1158,17 +1133,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>1992-01-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>1996-12-31</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>God förekomst</t>
+          <t>Burs 1:3</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1179,31 +1154,35 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Landsvägskant</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118251288</v>
+        <v>118251257</v>
       </c>
       <c r="B7" t="n">
-        <v>97869</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99093</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,37 +1190,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219847</v>
+        <v>219797</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Aurungs (Aurungs), Gtl</t>
+          <t>Aurungs, Aurungs, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>721233</v>
+        <v>721247</v>
       </c>
       <c r="R7" t="n">
         <v>6382420</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1302,15 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118250928</v>
+        <v>118251288</v>
       </c>
       <c r="B8" t="n">
-        <v>97733</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,37 +1292,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>49</v>
+        <v>219847</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Salepsrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Anacamptis pyramidalis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Aurungs (Aurungs), Gtl</t>
+          <t>Aurungs, Aurungs, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>721315</v>
+        <v>721233</v>
       </c>
       <c r="R8" t="n">
-        <v>6382524</v>
+        <v>6382420</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1378,6 +1352,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1401,6 +1380,200 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>118251035</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99145</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222118</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Flugblomster</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ophrys insectifera</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Aurungs, Aurungs, Gtl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>721315</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6382550</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>118251064</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99145</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222118</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Flugblomster</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ophrys insectifera</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Aurungs, Aurungs, Gtl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>721321</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6382481</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8265-2023 artfynd.xlsx
+++ b/artfynd/A 8265-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118250928</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118250963</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118251123</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118251170</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1176,6 +1201,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105082296</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118251257</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1380,6 +1415,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118251288</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1477,6 +1517,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118251035</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1574,8 +1619,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118251064</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>